--- a/resultant_excel.xlsx
+++ b/resultant_excel.xlsx
@@ -502,34 +502,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vinayak</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8107331777</t>
+          <t>8146994031</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>vinayak_sharma@technologymindz.com</t>
+          <t>bob.smith@example.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Alice is interested in the premium package that includes advanced analytics, priority support, and additional storage capacity. She wants a detailed demo before making the decision.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>no-answer</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>91</t>
@@ -537,65 +541,73 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ABC Company</t>
+          <t>B Company</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Texas, USA</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>"nan
+[2025-08-23 13:05:56] The customer, Bob Smith, is from the Automobile industry and wants to know how Technology Mindz can help him grow his company. The agent explains the services offered by Technology Mindz, including Salesforce implementation, robotic process automation, AI and data analytics, and cybersecurity solutions. The customer schedules a meeting with the agent for the next day at 5 p.m.
+[2025-08-23 13:22:09] No summary available. Conversation transcript missing."
+[2025-09-09 17:18:56] No summary available. Conversation transcript missing.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>nan
+[2025-09-09 17:18:56] No tasks found for this call.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vipul</t>
+          <t>Vinayak</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8407917181</t>
+          <t>7878994162</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>vinayak_sharma@technologymindz.com</t>
+          <t>alice.johnson@example.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Charlie is evaluating enterprise-level solutions with a strong emphasis on scalability, integration with his existing ERP system, and compliance with international data protection regulations. He also needs a custom training program for his team.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>91</t>
@@ -603,27 +615,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>XYZ Company Ltd.</t>
+          <t>D Company</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Texas, USA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Charlie has shown strong interest in a long-term partnership if the enterprise solution aligns with his company’s compliance and integration needs. He mentioned that decision-making will involve multiple stakeholders, and the procurement cycle might take up to three months. We should prepare detailed documentation, case studies, and a tailored presentation for his board of directors.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">

--- a/resultant_excel.xlsx
+++ b/resultant_excel.xlsx
@@ -502,7 +502,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>Anand Swarup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>bob.smith@example.com</t>
+          <t>anand_swarup@technologymindz.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>no-answer</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -564,19 +564,19 @@
           <t>"nan
 [2025-08-23 13:05:56] The customer, Bob Smith, is from the Automobile industry and wants to know how Technology Mindz can help him grow his company. The agent explains the services offered by Technology Mindz, including Salesforce implementation, robotic process automation, AI and data analytics, and cybersecurity solutions. The customer schedules a meeting with the agent for the next day at 5 p.m.
 [2025-08-23 13:22:09] No summary available. Conversation transcript missing."
-[2025-09-09 17:18:56] No summary available. Conversation transcript missing.</t>
+[2025-09-11 11:20:44] The user wants to schedule a meeting with the assistant for the next day at 5 p.m. and have a meeting invitation sent to their email.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>nan
-[2025-09-09 17:18:56] No tasks found for this call.</t>
+[2025-09-11 11:20:44] 1. Schedule a meeting, 2. Send a meeting invitation to the user's email</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7878994162</t>
+          <t>8107061392</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -635,12 +635,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>nan
+[2025-09-11 11:21:18] The agent introduced themselves and asked if it's a good time to talk to Vinayak from the Healthcare industry.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t xml:space="preserve">nan
+[2025-09-11 11:21:18] </t>
         </is>
       </c>
     </row>

--- a/resultant_excel.xlsx
+++ b/resultant_excel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -561,88 +561,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>"nan
-[2025-08-23 13:05:56] The customer, Bob Smith, is from the Automobile industry and wants to know how Technology Mindz can help him grow his company. The agent explains the services offered by Technology Mindz, including Salesforce implementation, robotic process automation, AI and data analytics, and cybersecurity solutions. The customer schedules a meeting with the agent for the next day at 5 p.m.
-[2025-08-23 13:22:09] No summary available. Conversation transcript missing."
-[2025-09-11 11:20:44] The user wants to schedule a meeting with the assistant for the next day at 5 p.m. and have a meeting invitation sent to their email.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nan
-[2025-09-11 11:20:44] 1. Schedule a meeting, 2. Send a meeting invitation to the user's email</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Vinayak</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8107061392</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>alice.johnson@example.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>D Company</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Texas, USA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nan
-[2025-09-11 11:21:18] The agent introduced themselves and asked if it's a good time to talk to Vinayak from the Healthcare industry.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nan
-[2025-09-11 11:21:18] </t>
         </is>
       </c>
     </row>
